--- a/data/03 Matches.xlsx
+++ b/data/03 Matches.xlsx
@@ -152,9 +152,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_matches" displayName="tbl_matches" ref="A1:N26" headerRowCount="1">
-  <autoFilter ref="A1:N26"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_matches" displayName="tbl_matches" ref="A1:V26" headerRowCount="1">
+  <autoFilter ref="A1:V26"/>
+  <tableColumns count="22">
     <tableColumn id="1" name="CU Number"/>
     <tableColumn id="2" name="Invoice Type"/>
     <tableColumn id="3" name="Amount Match"/>
@@ -165,10 +165,18 @@
     <tableColumn id="8" name="ERP Date"/>
     <tableColumn id="9" name="ERP Amount"/>
     <tableColumn id="10" name="ERP VAT"/>
-    <tableColumn id="11" name="KRA Invoice #"/>
-    <tableColumn id="12" name="KRA Date"/>
-    <tableColumn id="13" name="KRA Amount"/>
-    <tableColumn id="14" name="KRA VAT"/>
+    <tableColumn id="11" name="ERP 16% Base"/>
+    <tableColumn id="12" name="ERP 8% Base"/>
+    <tableColumn id="13" name="ERP 0% Base"/>
+    <tableColumn id="14" name="ERP Exempt Base"/>
+    <tableColumn id="15" name="KRA Invoice #"/>
+    <tableColumn id="16" name="KRA Date"/>
+    <tableColumn id="17" name="KRA Amount"/>
+    <tableColumn id="18" name="KRA VAT"/>
+    <tableColumn id="19" name="KRA 16% Base"/>
+    <tableColumn id="20" name="KRA 8% Base"/>
+    <tableColumn id="21" name="KRA 0% Base"/>
+    <tableColumn id="22" name="KRA Exempt Base"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -463,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -476,10 +484,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -535,22 +551,62 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>ERP 16% Base</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ERP 8% Base</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ERP 0% Base</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ERP Exempt Base</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>KRA Invoice #</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>KRA Date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>KRA Amount</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>KRA VAT</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>KRA 16% Base</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>KRA 8% Base</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>KRA 0% Base</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>KRA Exempt Base</t>
         </is>
       </c>
     </row>
@@ -599,23 +655,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="5" t="n">
+        <v>1801.72</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>0040563920002814274</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="n">
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="n">
         <v>1801.75</v>
       </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>1801.75</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -663,23 +743,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="5" t="n">
+        <v>2688.79</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>0040806140000136196</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="n">
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="n">
         <v>2688.79</v>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>2688.79</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -727,23 +831,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="5" t="n">
+        <v>129.31</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>0110610850000009873</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="n">
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="n">
         <v>129.31</v>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>129.31</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -791,23 +919,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="5" t="n">
+        <v>905.17</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>0170493130000181887</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="n">
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="n">
         <v>905.17</v>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>905.17</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -855,23 +1007,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="5" t="n">
+        <v>258.62</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>0171725760000090047</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="n">
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="n">
         <v>258.62</v>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>258.62</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -919,23 +1095,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>0190148290000004655</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="n">
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -983,23 +1183,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="5" t="n">
+        <v>92239.24000000001</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>0190434350000018670</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="n">
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="n">
         <v>92239.22</v>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>92239.22</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1047,23 +1271,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="5" t="n">
+        <v>15470</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>0190434350000018671</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="n">
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="n">
         <v>15470</v>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>15470</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1111,23 +1359,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="5" t="n">
+        <v>114137.93</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>0190450230000029005</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="n">
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n">
         <v>114137.93</v>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>114137.93</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1175,23 +1447,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>0191854130000000635</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="n">
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1239,23 +1535,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="5" t="n">
+        <v>258.62</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>0432185200000031423</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="n">
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n">
         <v>258.62</v>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>258.62</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1303,23 +1623,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>7462186815086648176</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="n">
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="n">
         <v>60000</v>
       </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1367,23 +1711,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="5" t="n">
+        <v>2585.35</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>7462187075087850991</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="n">
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="n">
         <v>2585.34</v>
       </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>2585.34</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1431,23 +1799,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="5" t="n">
+        <v>2585.35</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>7462187085087851020</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="n">
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="n">
         <v>2585.34</v>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>2585.34</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1495,23 +1887,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="5" t="n">
+        <v>4310.34</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>7462187165087851267</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="n">
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="n">
         <v>4310.34</v>
       </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>4310.34</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1559,23 +1975,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="5" t="n">
+        <v>5172.41</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>7462187175087441382</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="n">
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="n">
         <v>5172.41</v>
       </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>5172.41</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1623,23 +2063,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="5" t="n">
+        <v>2594.83</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>7462187555086647062</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="n">
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="n">
         <v>2594.83</v>
       </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>2594.83</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1687,23 +2151,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="5" t="n">
+        <v>4310.34</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>7462187555087850831</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="n">
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="n">
         <v>4310.34</v>
       </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>4310.34</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1751,23 +2239,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="5" t="n">
+        <v>11661.12</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>INV19061991</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="n">
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="n">
         <v>11661.12</v>
       </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>11661.12</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1815,23 +2327,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="5" t="n">
+        <v>3320</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>KRACU0100029824/838</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="n">
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="n">
         <v>3320</v>
       </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>3320</v>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1879,23 +2415,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>KRACU0100068638/16429</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="n">
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1943,23 +2503,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" s="5" t="n">
+        <v>4655.17</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>KRACU0200104934/113</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="n">
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="n">
         <v>4655.17</v>
       </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>4655.17</v>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2007,23 +2591,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K24" s="5" t="n">
+        <v>3448.85</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t>KRACU0300001459/1415189</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="n">
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="n">
         <v>3448.85</v>
       </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>3448.85</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2071,23 +2679,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="5" t="n">
+        <v>258.62</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>KRACU0300003082/216243</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="n">
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="n">
         <v>258.62</v>
       </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="n">
+        <v>258.62</v>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2135,23 +2767,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K26" s="5" t="n">
+        <v>3120</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>KRACU0400000391/19674</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="n">
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="n">
         <v>3120</v>
       </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>3120</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
